--- a/GoogleTest/CheckList/ShaderTest.xlsx
+++ b/GoogleTest/CheckList/ShaderTest.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\visualStudioPrograms\cyanoSimulation\GoogleTest\CheckList\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB6FAC1-1C85-43DB-9D9D-792371BC84C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,321 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+  <si>
+    <t>テスト項目</t>
+    <rPh sb="3" eb="5">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>意図する結果</t>
+    <rPh sb="0" eb="2">
+      <t>イト</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>関数</t>
+    <rPh sb="0" eb="2">
+      <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dispatch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>setStructuredBuffer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何も追加されていない場合、StructuredBufferが任意の位置に追加されるかのテスト</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すでに追加された場合に追加された際のテスト</t>
+    <rPh sb="3" eb="5">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>setRWStructuredBuffer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加に失敗した際の挙動のテスト</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何も追加されていない場合、RWStructuredBufferが任意の位置に追加されるかのテスト</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>setRootConstants</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何も追加されていない場合、データを追加した際の挙動</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4以上のバッファを追加した場合</t>
+    <rPh sb="1" eb="3">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4(4バイト×4)以上の要素を追加した場合</t>
+    <rPh sb="9" eb="11">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>clearRWStructuredBuffer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空のRWStructuredBufferを除去した場合の挙動</t>
+    <rPh sb="0" eb="1">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジョキョ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データがある場合、クリアした際の挙動</t>
+    <rPh sb="6" eb="8">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリアに失敗した際の挙動</t>
+    <rPh sb="4" eb="6">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何も起きない</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アサーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1DWordまでの要素が追加</t>
+    <rPh sb="9" eb="11">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データが初期化される</t>
+    <rPh sb="4" eb="7">
+      <t>ショキカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バッファの配置が適切でない場合の挙動</t>
+    <rPh sb="5" eb="7">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>適切にバッファが配置された場合の挙動</t>
+    <rPh sb="0" eb="2">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計算が行われる</t>
+    <rPh sb="0" eb="2">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンストラクタ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PSO、ルートシグネチャの作成、ディスクリプタヒープにビューを追加</t>
+    <rPh sb="13" eb="15">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,13 +346,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,11 +380,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +665,174 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="42.8984375" customWidth="1"/>
+    <col min="2" max="2" width="86.59765625" customWidth="1"/>
+    <col min="3" max="3" width="39.19921875" customWidth="1"/>
+    <col min="4" max="4" width="38.296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2"/>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2"/>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2"/>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2"/>
+      <c r="B13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2"/>
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A15"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>